--- a/Paket_5_Matematika_TKA_SD.xlsx
+++ b/Paket_5_Matematika_TKA_SD.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Paket 5 Matematika" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -471,27 +471,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>[Paket 5] Soal Matematika 1: contoh soal numerasi sederhana.</t>
+          <t>Arman menabung di celengan setiap hari selama 4 minggu. Setiap hari Senin sampai Jumat ia menabung Rp5.000, sedangkan hari Sabtu dan Minggu ia menabung Rp8.000. Setelah 4 minggu, Arman mengambil uang celengannya sebanyak Rp75.000 untuk membeli tas sekolah. Berapakah sisa uang tabungan Arman sekarang?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  Rp89.000</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  Rp92.000</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  Rp95.000</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  Rp105.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -502,7 +502,11 @@
       <c r="H2" t="n">
         <v>60</v>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -512,27 +516,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>[Paket 5] Soal Matematika 2: contoh soal numerasi sederhana.</t>
+          <t>Seekor burung camar terbang pada ketinggian 15 meter di atas permukaan laut. Tepat di bawah burung tersebut, seekor lumba-lumba berenang pada kedalaman 6 meter di bawah permukaan laut. Berapakah jarak tegak lurus antara burung camar dan lumba-lumba tersebut?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  9 meter</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  18 meter</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  21 meter</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  24 meter</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -543,7 +547,11 @@
       <c r="H3" t="n">
         <v>60</v>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -553,27 +561,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>[Paket 5] Soal Matematika 3: contoh soal numerasi sederhana.</t>
+          <t>Sebuah botol berisi madu murni sebanyak 4/5 liter. Setiap hari adik meminum madu tersebut sebanyak 1/15 liter. Dalam berapa harikah madu murni di dalam botol tersebut akan habis?</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  10 hari</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  12 hari</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  14 hari</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  15 hari</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -584,7 +592,11 @@
       <c r="H4" t="n">
         <v>60</v>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -594,27 +606,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>[Paket 5] Soal Matematika 4: contoh soal numerasi sederhana.</t>
+          <t>Perbandingan banyak kelereng Andi dan Budi adalah 2 : 3, sedangkan perbandingan kelereng Budi dan Candra adalah 4 : 5. Jika jumlah kelereng mereka bertiga adalah 70 butir, banyak kelereng yang dimiliki Budi adalah....</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  16 butir</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  24 butir</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  30 butir</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  35 butir</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -625,37 +637,42 @@
       <c r="H5" t="n">
         <v>60</v>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Multiple Choice</t>
+          <t>Multiple</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>[Paket 5] Soal Matematika 5: contoh soal numerasi sederhana.</t>
+          <t>Kelompok tani Makmur memiliki 45 bibit cabai rawit, 60 bibit terung, dan 75 bibit tomat. Bibit-bibit ini akan dibagikan kepada sejumlah kelompok dasawisma dengan jumlah masing-masing bibit sama banyak tanpa sisa.
+Manakah pernyataan berikut yang BENAR?  [Pilihan Ganda Kompleks: Jawaban benar lebih dari satu]</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  Jumlah kelompok dasawisma terbanyak yang dapat menerima bibit adalah 15 kelompok.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  Setiap kelompok dasawisma menerima 3 bibit cabai rawit.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  Setiap kelompok dasawisma menerima 4 bibit terung.</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  Setiap kelompok dasawisma menerima 6 bibit tomat.</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -666,7 +683,11 @@
       <c r="H6" t="n">
         <v>60</v>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -676,27 +697,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>[Paket 5] Soal Matematika 6: contoh soal numerasi sederhana.</t>
+          <t>Hasil perhitungan dari 15² - √576 + ∛4.096 adalah....</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  215</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  217</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  225</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  233</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -707,17 +728,21 @@
       <c r="H7" t="n">
         <v>60</v>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Multiple Choice</t>
+          <t>Multiple</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>[Paket 5] Soal Matematika 7: contoh soal numerasi sederhana.</t>
+          <t>Tentukan nilai kebenaran dari pernyataan kesetaraan nilai pecahan berikut!  [Pilihan Ganda Kompleks: Kategori Benar / Salah]</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -748,7 +773,11 @@
       <c r="H8" t="n">
         <v>60</v>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -758,27 +787,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>[Paket 5] Soal Matematika 8: contoh soal numerasi sederhana.</t>
+          <t>Seorang pasien di rumah sakit harus meminum obat kapsul setiap 4 jam sekali dan obat sirup setiap 6 jam sekali. Jika pasien tersebut meminum kedua obat bersamaan pada pukul 08.00 pagi, pukul berapakah ia akan meminum kedua obat tersebut bersamaan lagi untuk waktu berikutnya?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  16.00 WIB</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  18.00 WIB</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  20.00 WIB</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  22.00 WIB</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -789,7 +818,11 @@
       <c r="H9" t="n">
         <v>60</v>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -799,27 +832,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>[Paket 5] Soal Matematika 9: contoh soal numerasi sederhana.</t>
+          <t>Denah ruang kamar tidur berbentuk persegi berukuran 3 cm x 3 cm dengan skala 1 : 100. Lantai kamar tidur sebenarnya akan dipasangi ubin dengan biaya pemasangan Rp40.000 per meter persegi. Berapakah biaya pemasangan ubin seluruh lantai kamar tidur tersebut?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  Rp240.000</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  Rp320.000</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  Rp360.000</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  Rp400.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -830,7 +863,11 @@
       <c r="H10" t="n">
         <v>60</v>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -840,27 +877,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>[Paket 5] Soal Matematika 10: contoh soal numerasi sederhana.</t>
+          <t>Sebuah penampungan air minum berisi 2,5 m³ air. Air tersebut dialirkan ke dalam jeriken sebanyak 450 liter dan dikemas ke dalam botol sebanyak 650 dm³. Berapakah sisa air di dalam penampungan tersebut dalam satuan liter?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  1.400 liter</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  1.450 liter</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  1.500 liter</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  1.600 liter</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -871,7 +908,11 @@
       <c r="H11" t="n">
         <v>60</v>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -881,27 +922,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>[Paket 5] Soal Matematika 11: contoh soal numerasi sederhana.</t>
+          <t>Sebuah galon air mineral berukuran 19 liter diisi dari kran depo air minum sampai penuh dalam waktu 2 menit. Debit aliran air dari kran tersebut adalah....</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  8,5 liter/menit</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  9,0 liter/menit</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  9,5 liter/menit</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  10,0 liter/menit</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -912,37 +953,41 @@
       <c r="H12" t="n">
         <v>60</v>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Multiple Choice</t>
+          <t>Multiple</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>[Paket 5] Soal Matematika 12: contoh soal numerasi sederhana.</t>
+          <t>Perhatikan bangun ruang kubus dan balok. Manakah pernyataan berikut yang bernilai BENAR untuk KEDUA bangun ruang tersebut?  [Pilihan Ganda Kompleks: Jawaban benar lebih dari satu]</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  Keduanya memiliki 6 bidang sisi dan 8 titik sudut.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  Keduanya memiliki 12 rusuk.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  Keduanya memiliki 4 buah diagonal ruang.</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  Semua sisi pada kedua bangun ruang tersebut selalu berbentuk persegi.</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -953,7 +998,11 @@
       <c r="H13" t="n">
         <v>60</v>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -963,27 +1012,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>[Paket 5] Soal Matematika 13: contoh soal numerasi sederhana.</t>
+          <t>Sebuah kotak kayu tanpa tutup memiliki ukuran panjang 50 cm, lebar 40 cm, dan tinggi 30 cm. Luas permukaan kayu yang dibutuhkan untuk membuat kotak tanpa tutup tersebut adalah....</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  5.400 cm²</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  7.400 cm²</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  8.400 cm²</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  9.400 cm²</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -994,7 +1043,11 @@
       <c r="H14" t="n">
         <v>60</v>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1004,27 +1057,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>[Paket 5] Soal Matematika 14: contoh soal numerasi sederhana.</t>
+          <t>Sebuah cetakan nasi tumpeng berbentuk kerucut memiliki jari-jari lingkaran alas 7 cm dan tinggi kerucut 24 cm. (Gunakan π = 22/7). Volume nasi tumpeng yang dapat dicetak adalah....</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  1.124 cm³</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  1.232 cm³</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  1.456 cm³</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  3.696 cm³</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1035,17 +1088,21 @@
       <c r="H15" t="n">
         <v>60</v>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Multiple Choice</t>
+          <t>Multiple</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>[Paket 5] Soal Matematika 15: contoh soal numerasi sederhana.</t>
+          <t>Tentukan kebenaran dari prinsip proyeksi dan visualisasi spasial berikut!  [Pilihan Ganda Kompleks: Kategori Benar / Salah]</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1076,7 +1133,11 @@
       <c r="H16" t="n">
         <v>60</v>
       </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1086,27 +1147,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>[Paket 5] Soal Matematika 16: contoh soal numerasi sederhana.</t>
+          <t>Data penimbangan berat badan (dalam kg) lima balita di Posyandu Melati adalah: 11,5 kg; 12,0 kg; 10,5 kg; 13,0 kg; dan 11,0 kg. Rata-rata berat badan balita tersebut adalah....</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  11,4 kg</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  11,6 kg</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  11,8 kg</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  12,0 kg</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1117,7 +1178,11 @@
       <c r="H17" t="n">
         <v>60</v>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1127,27 +1192,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>[Paket 5] Soal Matematika 17: contoh soal numerasi sederhana.</t>
+          <t>Hasil lompatan jauh (dalam meter) seorang atlet pada 7 kali percobaan latihan adalah: 4,8 m; 5,2 m; 4,9 m; 5,4 m; 5,0 m; 5,1 m; dan 5,3 m. Nilai median dari hasil lompatan tersebut adalah....</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  5,0 meter</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  5,1 meter</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  5,2 meter</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  5,3 meter</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1158,37 +1223,42 @@
       <c r="H18" t="n">
         <v>60</v>
       </c>
-      <c r="I18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Multiple Choice</t>
+          <t>Multiple</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>[Paket 5] Soal Matematika 18: contoh soal numerasi sederhana.</t>
+          <t>Data panen sayuran hidroponik sekolah mencatat: Bayam (24 kg), Selada (18 kg), Kangkung (30 kg), dan Pakcoy (28 kg).
+Manakah pernyataan analisis data berikut yang BENAR?  [Pilihan Ganda Kompleks: Jawaban benar lebih dari satu]</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  Total seluruh panen sayuran adalah 100 kg.</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  Kangkung merupakan sayuran dengan hasil panen paling banyak (modus).</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  Selisih panen kangkung dan selada adalah 12 kg.</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  Persentase panen bayam terhadap seluruh hasil panen adalah 25%.</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1199,7 +1269,11 @@
       <c r="H19" t="n">
         <v>60</v>
       </c>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1209,27 +1283,32 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>[Paket 5] Soal Matematika 19: contoh soal numerasi sederhana.</t>
+          <t>Sebuah diagram lingkaran menyajikan data cara transportasi 200 siswa menuju sekolah:
+• Jalan kaki: 20%
+• Naik sepeda: 35%
+• Diantar sepeda motor: 30%
+• Sisanya naik angkutan umum
+Banyak siswa yang berangkat sekolah menggunakan angkutan umum adalah....</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  25 orang</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  30 orang</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  35 orang</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  40 orang</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1240,17 +1319,21 @@
       <c r="H20" t="n">
         <v>60</v>
       </c>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Multiple Choice</t>
+          <t>Multiple</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>[Paket 5] Soal Matematika 20: contoh soal numerasi sederhana.</t>
+          <t>Perhatikan barisan pola bilangan segitiga: 1, 3, 6, 10, 15, 21, ... Tentukan kebenaran dari pernyataan berikut!  [Pilihan Ganda Kompleks: Kategori Benar / Salah]</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1281,7 +1364,11 @@
       <c r="H21" t="n">
         <v>60</v>
       </c>
-      <c r="I21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
